--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_80/per_file_predictions_epoch_80.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_80/per_file_predictions_epoch_80.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8127,0.1918,0.0285,0.0035</t>
-  </si>
-  <si>
-    <t>0.9253,0.0266,0.0296,0.0049</t>
-  </si>
-  <si>
-    <t>0.7275,0.3136,0.0209,0.0015</t>
-  </si>
-  <si>
-    <t>0.9561,0.0141,0.0014,0.0026</t>
-  </si>
-  <si>
-    <t>0.9461,0.0447,0.0018,0.0005</t>
-  </si>
-  <si>
-    <t>0.9557,0.0413,0.0012,0.0008</t>
-  </si>
-  <si>
-    <t>0.9668,0.0328,0.0012,0.0005</t>
-  </si>
-  <si>
-    <t>0.9650,0.0221,0.0020,0.0016</t>
-  </si>
-  <si>
-    <t>0.8083,0.2682,0.0069,0.0007</t>
-  </si>
-  <si>
-    <t>0.9029,0.1058,0.0057,0.0010</t>
-  </si>
-  <si>
-    <t>0.9277,0.0643,0.0034,0.0021</t>
-  </si>
-  <si>
-    <t>0.9258,0.0636,0.0031,0.0019</t>
-  </si>
-  <si>
-    <t>0.9798,0.0062,0.0085,0.0001</t>
-  </si>
-  <si>
-    <t>0.9206,0.0547,0.0237,0.0007</t>
-  </si>
-  <si>
-    <t>0.8855,0.0146,0.1191,0.0005</t>
-  </si>
-  <si>
-    <t>0.8237,0.0142,0.2545,0.0020</t>
-  </si>
-  <si>
-    <t>0.8999,0.0940,0.0164,0.0009</t>
-  </si>
-  <si>
-    <t>0.9142,0.1275,0.0039,0.0002</t>
-  </si>
-  <si>
-    <t>0.9190,0.1487,0.0025,0.0002</t>
-  </si>
-  <si>
-    <t>0.8330,0.2658,0.0057,0.0004</t>
-  </si>
-  <si>
-    <t>0.8548,0.2546,0.0029,0.0002</t>
-  </si>
-  <si>
-    <t>0.5535,0.6315,0.0060,0.0002</t>
-  </si>
-  <si>
-    <t>0.9673,0.0199,0.0080,0.0003</t>
-  </si>
-  <si>
-    <t>0.9933,0.0010,0.0050,0.0001</t>
-  </si>
-  <si>
-    <t>0.9163,0.0085,0.0953,0.0014</t>
-  </si>
-  <si>
-    <t>0.9422,0.0274,0.0216,0.0008</t>
-  </si>
-  <si>
-    <t>0.9504,0.0064,0.0618,0.0007</t>
-  </si>
-  <si>
-    <t>0.8142,0.0185,0.2659,0.0022</t>
-  </si>
-  <si>
-    <t>0.6549,0.0241,0.4001,0.0013</t>
-  </si>
-  <si>
-    <t>0.9273,0.0799,0.0081,0.0008</t>
-  </si>
-  <si>
-    <t>0.9177,0.0852,0.0049,0.0004</t>
-  </si>
-  <si>
-    <t>0.0710,0.1790,0.8913,0.0021</t>
-  </si>
-  <si>
-    <t>0.8520,0.1536,0.0143,0.0004</t>
-  </si>
-  <si>
-    <t>0.8659,0.1294,0.0066,0.0017</t>
-  </si>
-  <si>
-    <t>0.9449,0.0382,0.0085,0.0019</t>
-  </si>
-  <si>
-    <t>0.9065,0.1506,0.0022,0.0003</t>
-  </si>
-  <si>
-    <t>0.9958,0.0025,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.3422,0.0498,0.5261,0.0011</t>
-  </si>
-  <si>
-    <t>0.9956,0.0001,0.0056,0.0001</t>
-  </si>
-  <si>
-    <t>0.9740,0.0050,0.0261,0.0006</t>
-  </si>
-  <si>
-    <t>0.8955,0.0149,0.1187,0.0015</t>
-  </si>
-  <si>
-    <t>0.6536,0.0962,0.1458,0.0010</t>
-  </si>
-  <si>
-    <t>0.4718,0.0653,0.2081,0.0002</t>
-  </si>
-  <si>
-    <t>0.9419,0.0026,0.0962,0.0011</t>
-  </si>
-  <si>
-    <t>0.9177,0.0994,0.0067,0.0003</t>
-  </si>
-  <si>
-    <t>0.9490,0.0459,0.0042,0.0001</t>
-  </si>
-  <si>
-    <t>0.9831,0.0088,0.0039,0.0001</t>
-  </si>
-  <si>
-    <t>0.8632,0.1784,0.0045,0.0001</t>
-  </si>
-  <si>
-    <t>0.2084,0.0307,0.8124,0.0031</t>
-  </si>
-  <si>
-    <t>0.5759,0.0138,0.5003,0.0016</t>
-  </si>
-  <si>
-    <t>0.9582,0.0034,0.0650,0.0004</t>
-  </si>
-  <si>
-    <t>0.7476,0.0098,0.3823,0.0042</t>
-  </si>
-  <si>
-    <t>0.0729,0.0116,0.9357,0.0011</t>
-  </si>
-  <si>
-    <t>0.7696,0.0356,0.1832,0.0006</t>
-  </si>
-  <si>
-    <t>0.8545,0.1982,0.0050,0.0008</t>
-  </si>
-  <si>
-    <t>0.6300,0.3715,0.0245,0.0048</t>
-  </si>
-  <si>
-    <t>0.9746,0.0208,0.0019,0.0007</t>
-  </si>
-  <si>
-    <t>0.2595,0.5310,0.3516,0.0065</t>
-  </si>
-  <si>
-    <t>0.8719,0.1246,0.0032,0.0015</t>
-  </si>
-  <si>
-    <t>0.9542,0.0424,0.0014,0.0009</t>
-  </si>
-  <si>
-    <t>0.8514,0.1859,0.0077,0.0009</t>
-  </si>
-  <si>
-    <t>0.1928,0.1546,0.6810,0.0036</t>
-  </si>
-  <si>
-    <t>0.3355,0.0095,0.8498,0.0005</t>
-  </si>
-  <si>
-    <t>0.6435,0.2167,0.1037,0.0014</t>
-  </si>
-  <si>
-    <t>0.1521,0.3231,0.5482,0.0013</t>
-  </si>
-  <si>
-    <t>0.0404,0.0285,0.9613,0.0018</t>
-  </si>
-  <si>
-    <t>0.9725,0.0343,0.0025,0.0000</t>
-  </si>
-  <si>
-    <t>0.0889,0.9430,0.0033,0.0001</t>
-  </si>
-  <si>
-    <t>0.8196,0.1944,0.0187,0.0007</t>
-  </si>
-  <si>
-    <t>0.7934,0.2277,0.0139,0.0006</t>
-  </si>
-  <si>
-    <t>0.1020,0.7638,0.3737,0.0017</t>
-  </si>
-  <si>
-    <t>0.6405,0.0953,0.1525,0.0013</t>
-  </si>
-  <si>
-    <t>0.9096,0.0147,0.0702,0.0002</t>
-  </si>
-  <si>
-    <t>0.1864,0.8409,0.0056,0.0001</t>
-  </si>
-  <si>
-    <t>0.0469,0.8673,0.4965,0.0020</t>
-  </si>
-  <si>
-    <t>0.9797,0.0059,0.0056,0.0023</t>
-  </si>
-  <si>
-    <t>0.8479,0.0365,0.0260,0.0389</t>
-  </si>
-  <si>
-    <t>0.9699,0.0090,0.0035,0.0035</t>
-  </si>
-  <si>
-    <t>0.9347,0.0399,0.0131,0.0038</t>
-  </si>
-  <si>
-    <t>0.9515,0.0213,0.0114,0.0037</t>
-  </si>
-  <si>
-    <t>0.9801,0.0060,0.0021,0.0016</t>
-  </si>
-  <si>
-    <t>0.8468,0.0450,0.0782,0.0008</t>
-  </si>
-  <si>
-    <t>0.6066,0.0271,0.3670,0.0013</t>
-  </si>
-  <si>
-    <t>0.8689,0.0181,0.1354,0.0005</t>
-  </si>
-  <si>
-    <t>0.9699,0.0095,0.0186,0.0002</t>
-  </si>
-  <si>
-    <t>0.7448,0.0286,0.2199,0.0007</t>
-  </si>
-  <si>
-    <t>0.8899,0.0850,0.0256,0.0002</t>
-  </si>
-  <si>
-    <t>0.8328,0.2252,0.0085,0.0012</t>
-  </si>
-  <si>
-    <t>0.9208,0.0792,0.0018,0.0008</t>
-  </si>
-  <si>
-    <t>0.9304,0.0620,0.0027,0.0010</t>
-  </si>
-  <si>
-    <t>0.9505,0.0466,0.0030,0.0011</t>
-  </si>
-  <si>
-    <t>0.8368,0.2140,0.0053,0.0009</t>
-  </si>
-  <si>
-    <t>0.8924,0.1288,0.0056,0.0011</t>
-  </si>
-  <si>
-    <t>0.9165,0.0692,0.0032,0.0019</t>
-  </si>
-  <si>
-    <t>0.9015,0.1275,0.0030,0.0009</t>
-  </si>
-  <si>
-    <t>0.9656,0.0335,0.0009,0.0005</t>
-  </si>
-  <si>
-    <t>0.8793,0.1473,0.0064,0.0011</t>
-  </si>
-  <si>
-    <t>0.9284,0.0567,0.0023,0.0017</t>
-  </si>
-  <si>
-    <t>0.6836,0.3831,0.0077,0.0021</t>
-  </si>
-  <si>
-    <t>0.9635,0.0177,0.0009,0.0018</t>
-  </si>
-  <si>
-    <t>0.8625,0.1575,0.0043,0.0020</t>
-  </si>
-  <si>
-    <t>0.9744,0.0203,0.0015,0.0008</t>
-  </si>
-  <si>
-    <t>0.7972,0.2316,0.0132,0.0027</t>
-  </si>
-  <si>
-    <t>0.0600,0.0582,0.9468,0.0009</t>
-  </si>
-  <si>
-    <t>0.9112,0.0137,0.0966,0.0004</t>
-  </si>
-  <si>
-    <t>0.9779,0.0062,0.0084,0.0001</t>
-  </si>
-  <si>
-    <t>0.9639,0.0052,0.0343,0.0010</t>
-  </si>
-  <si>
-    <t>0.1326,0.9122,0.0071,0.0005</t>
-  </si>
-  <si>
-    <t>0.3259,0.7618,0.0159,0.0007</t>
-  </si>
-  <si>
-    <t>0.8468,0.2218,0.0067,0.0004</t>
-  </si>
-  <si>
-    <t>0.9326,0.0787,0.0043,0.0005</t>
-  </si>
-  <si>
-    <t>0.3937,0.7327,0.0137,0.0005</t>
-  </si>
-  <si>
-    <t>0.7570,0.3854,0.0024,0.0002</t>
-  </si>
-  <si>
-    <t>0.7833,0.3095,0.0104,0.0007</t>
-  </si>
-  <si>
-    <t>0.9399,0.0419,0.0105,0.0006</t>
-  </si>
-  <si>
-    <t>0.9075,0.0190,0.0935,0.0025</t>
-  </si>
-  <si>
-    <t>0.6766,0.3749,0.0200,0.0008</t>
-  </si>
-  <si>
-    <t>0.9196,0.0489,0.0322,0.0007</t>
-  </si>
-  <si>
-    <t>0.9113,0.0953,0.0118,0.0010</t>
-  </si>
-  <si>
-    <t>0.8825,0.1528,0.0067,0.0001</t>
-  </si>
-  <si>
-    <t>0.9110,0.1330,0.0016,0.0000</t>
-  </si>
-  <si>
-    <t>0.9346,0.0801,0.0043,0.0001</t>
-  </si>
-  <si>
-    <t>0.2930,0.3377,0.1374,0.0003</t>
-  </si>
-  <si>
-    <t>0.9842,0.0207,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9325,0.0604,0.0042,0.0007</t>
-  </si>
-  <si>
-    <t>0.8614,0.1733,0.0026,0.0008</t>
-  </si>
-  <si>
-    <t>0.9240,0.1078,0.0022,0.0003</t>
-  </si>
-  <si>
-    <t>0.9493,0.0686,0.0020,0.0006</t>
-  </si>
-  <si>
-    <t>0.7588,0.2972,0.0058,0.0010</t>
-  </si>
-  <si>
-    <t>0.8106,0.2196,0.0097,0.0024</t>
-  </si>
-  <si>
-    <t>0.8794,0.1570,0.0043,0.0009</t>
-  </si>
-  <si>
-    <t>0.9708,0.0219,0.0035,0.0006</t>
-  </si>
-  <si>
-    <t>0.9422,0.0607,0.0060,0.0006</t>
-  </si>
-  <si>
-    <t>0.9105,0.0956,0.0047,0.0014</t>
-  </si>
-  <si>
-    <t>0.8165,0.0142,0.2421,0.0012</t>
-  </si>
-  <si>
-    <t>0.9242,0.0144,0.0691,0.0003</t>
-  </si>
-  <si>
-    <t>0.8220,0.0068,0.2263,0.0005</t>
-  </si>
-  <si>
-    <t>0.6458,0.0881,0.2528,0.0023</t>
-  </si>
-  <si>
-    <t>0.9931,0.0018,0.0020,0.0001</t>
-  </si>
-  <si>
-    <t>0.9508,0.0274,0.0108,0.0011</t>
-  </si>
-  <si>
-    <t>0.9095,0.0216,0.0837,0.0030</t>
-  </si>
-  <si>
-    <t>0.9606,0.0179,0.0089,0.0005</t>
-  </si>
-  <si>
-    <t>0.9661,0.0169,0.0052,0.0016</t>
-  </si>
-  <si>
-    <t>0.9729,0.0024,0.0052,0.0060</t>
-  </si>
-  <si>
-    <t>0.9661,0.0032,0.0070,0.0072</t>
-  </si>
-  <si>
-    <t>0.9823,0.0046,0.0014,0.0014</t>
-  </si>
-  <si>
-    <t>0.1514,0.8963,0.0079,0.0002</t>
-  </si>
-  <si>
-    <t>0.9439,0.0651,0.0018,0.0006</t>
-  </si>
-  <si>
-    <t>0.6052,0.5263,0.0138,0.0016</t>
-  </si>
-  <si>
-    <t>0.9187,0.1050,0.0012,0.0005</t>
-  </si>
-  <si>
-    <t>0.9707,0.0216,0.0009,0.0005</t>
-  </si>
-  <si>
-    <t>0.8772,0.1357,0.0081,0.0011</t>
-  </si>
-  <si>
-    <t>0.9795,0.0092,0.0030,0.0010</t>
-  </si>
-  <si>
-    <t>0.7314,0.3376,0.0111,0.0020</t>
-  </si>
-  <si>
-    <t>0.4225,0.0506,0.5919,0.0546</t>
-  </si>
-  <si>
-    <t>0.9516,0.0234,0.0018,0.0019</t>
-  </si>
-  <si>
-    <t>0.9303,0.0392,0.0034,0.0028</t>
-  </si>
-  <si>
-    <t>0.9250,0.0907,0.0046,0.0003</t>
-  </si>
-  <si>
-    <t>0.9651,0.0240,0.0025,0.0007</t>
-  </si>
-  <si>
-    <t>0.9129,0.1143,0.0068,0.0004</t>
-  </si>
-  <si>
-    <t>0.8182,0.1534,0.0294,0.0022</t>
-  </si>
-  <si>
-    <t>0.8386,0.1849,0.0148,0.0006</t>
-  </si>
-  <si>
-    <t>0.8999,0.1283,0.0076,0.0003</t>
-  </si>
-  <si>
-    <t>0.8591,0.1171,0.0097,0.0036</t>
-  </si>
-  <si>
-    <t>0.9257,0.0954,0.0030,0.0006</t>
-  </si>
-  <si>
-    <t>0.9219,0.0531,0.0014,0.0014</t>
-  </si>
-  <si>
-    <t>0.9420,0.0552,0.0010,0.0008</t>
-  </si>
-  <si>
-    <t>0.9473,0.0403,0.0031,0.0019</t>
-  </si>
-  <si>
-    <t>0.9536,0.0485,0.0032,0.0007</t>
-  </si>
-  <si>
-    <t>0.8208,0.2173,0.0060,0.0011</t>
-  </si>
-  <si>
-    <t>0.8930,0.1280,0.0090,0.0011</t>
-  </si>
-  <si>
-    <t>0.9272,0.0733,0.0056,0.0006</t>
-  </si>
-  <si>
-    <t>0.7154,0.4060,0.0053,0.0008</t>
-  </si>
-  <si>
-    <t>0.8151,0.2772,0.0055,0.0006</t>
-  </si>
-  <si>
-    <t>0.9848,0.0151,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.6572,0.4988,0.0054,0.0007</t>
-  </si>
-  <si>
-    <t>0.7157,0.4140,0.0150,0.0010</t>
-  </si>
-  <si>
-    <t>0.9128,0.0614,0.0101,0.0019</t>
-  </si>
-  <si>
-    <t>0.5039,0.6038,0.0105,0.0010</t>
-  </si>
-  <si>
-    <t>0.0013,0.7165,0.9690,0.0001</t>
-  </si>
-  <si>
-    <t>0.9240,0.0865,0.0049,0.0013</t>
-  </si>
-  <si>
-    <t>0.3644,0.0174,0.6905,0.0026</t>
-  </si>
-  <si>
-    <t>0.8091,0.0052,0.3663,0.0007</t>
-  </si>
-  <si>
-    <t>0.9637,0.0094,0.0295,0.0004</t>
-  </si>
-  <si>
-    <t>0.0392,0.1721,0.9249,0.0014</t>
-  </si>
-  <si>
-    <t>0.3385,0.0747,0.6906,0.0060</t>
-  </si>
-  <si>
-    <t>0.4500,0.0132,0.6679,0.0018</t>
-  </si>
-  <si>
-    <t>0.9619,0.0022,0.0633,0.0007</t>
-  </si>
-  <si>
-    <t>0.9942,0.0011,0.0028,0.0001</t>
-  </si>
-  <si>
-    <t>0.8212,0.0932,0.0969,0.0031</t>
-  </si>
-  <si>
-    <t>0.8979,0.0781,0.0296,0.0016</t>
-  </si>
-  <si>
-    <t>0.8799,0.0704,0.0379,0.0011</t>
-  </si>
-  <si>
-    <t>0.7404,0.1779,0.0261,0.0003</t>
-  </si>
-  <si>
-    <t>0.9619,0.0093,0.0203,0.0009</t>
-  </si>
-  <si>
-    <t>0.9462,0.0390,0.0090,0.0007</t>
-  </si>
-  <si>
-    <t>0.9756,0.0042,0.0173,0.0005</t>
-  </si>
-  <si>
-    <t>0.8696,0.2159,0.0038,0.0004</t>
-  </si>
-  <si>
-    <t>0.6537,0.5524,0.0065,0.0004</t>
-  </si>
-  <si>
-    <t>0.9193,0.1042,0.0041,0.0007</t>
-  </si>
-  <si>
-    <t>0.6991,0.4535,0.0030,0.0003</t>
-  </si>
-  <si>
-    <t>0.9391,0.0746,0.0028,0.0004</t>
-  </si>
-  <si>
-    <t>0.9542,0.0252,0.0098,0.0004</t>
-  </si>
-  <si>
-    <t>0.9281,0.0450,0.0129,0.0005</t>
-  </si>
-  <si>
-    <t>0.9463,0.0102,0.0448,0.0025</t>
-  </si>
-  <si>
-    <t>0.9840,0.0042,0.0074,0.0004</t>
-  </si>
-  <si>
-    <t>0.8673,0.0409,0.0821,0.0023</t>
-  </si>
-  <si>
-    <t>0.0232,0.1968,0.9447,0.0030</t>
-  </si>
-  <si>
-    <t>0.9791,0.0040,0.0152,0.0003</t>
-  </si>
-  <si>
-    <t>0.9919,0.0010,0.0068,0.0002</t>
-  </si>
-  <si>
-    <t>0.8174,0.0111,0.2373,0.0010</t>
-  </si>
-  <si>
-    <t>0.8775,0.0147,0.1771,0.0009</t>
-  </si>
-  <si>
-    <t>0.9037,0.1230,0.0044,0.0007</t>
-  </si>
-  <si>
-    <t>0.9829,0.0165,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.8873,0.1334,0.0054,0.0009</t>
-  </si>
-  <si>
-    <t>0.7347,0.4092,0.0040,0.0005</t>
-  </si>
-  <si>
-    <t>0.9023,0.0820,0.0043,0.0019</t>
-  </si>
-  <si>
-    <t>0.8224,0.2222,0.0088,0.0012</t>
-  </si>
-  <si>
-    <t>0.8923,0.1114,0.0045,0.0016</t>
-  </si>
-  <si>
-    <t>0.8203,0.2413,0.0099,0.0012</t>
-  </si>
-  <si>
-    <t>0.6840,0.2259,0.0762,0.0022</t>
-  </si>
-  <si>
-    <t>0.7724,0.2147,0.0343,0.0014</t>
-  </si>
-  <si>
-    <t>0.8922,0.1278,0.0095,0.0008</t>
-  </si>
-  <si>
-    <t>0.0119,0.0125,0.9870,0.0004</t>
-  </si>
-  <si>
-    <t>0.0502,0.2535,0.8634,0.0018</t>
-  </si>
-  <si>
-    <t>0.2713,0.0471,0.8177,0.0009</t>
-  </si>
-  <si>
-    <t>0.5803,0.0395,0.4753,0.0020</t>
-  </si>
-  <si>
-    <t>0.7475,0.0074,0.3111,0.0005</t>
-  </si>
-  <si>
-    <t>0.0225,0.0165,0.9715,0.0012</t>
-  </si>
-  <si>
-    <t>0.9701,0.0052,0.0277,0.0002</t>
-  </si>
-  <si>
-    <t>0.9371,0.0347,0.0257,0.0013</t>
-  </si>
-  <si>
-    <t>0.9750,0.0054,0.0129,0.0003</t>
-  </si>
-  <si>
-    <t>0.9749,0.0062,0.0160,0.0004</t>
-  </si>
-  <si>
-    <t>0.9863,0.0058,0.0043,0.0001</t>
-  </si>
-  <si>
-    <t>0.9768,0.0219,0.0007,0.0005</t>
-  </si>
-  <si>
-    <t>0.9301,0.0802,0.0025,0.0010</t>
-  </si>
-  <si>
-    <t>0.8756,0.1393,0.0033,0.0013</t>
-  </si>
-  <si>
-    <t>0.9443,0.0769,0.0019,0.0004</t>
-  </si>
-  <si>
-    <t>0.9559,0.0293,0.0010,0.0011</t>
-  </si>
-  <si>
-    <t>0.9175,0.0808,0.0020,0.0009</t>
-  </si>
-  <si>
-    <t>0.9229,0.0820,0.0040,0.0011</t>
-  </si>
-  <si>
-    <t>0.9585,0.0445,0.0015,0.0007</t>
-  </si>
-  <si>
-    <t>0.7282,0.0953,0.0623,0.0003</t>
-  </si>
-  <si>
-    <t>0.3576,0.0290,0.5842,0.0004</t>
-  </si>
-  <si>
-    <t>0.2991,0.0849,0.6587,0.0027</t>
-  </si>
-  <si>
-    <t>0.9764,0.0060,0.0157,0.0005</t>
-  </si>
-  <si>
-    <t>0.8995,0.0026,0.2191,0.0008</t>
-  </si>
-  <si>
-    <t>0.9453,0.0216,0.0316,0.0010</t>
-  </si>
-  <si>
-    <t>0.8823,0.0164,0.1629,0.0031</t>
-  </si>
-  <si>
-    <t>0.9735,0.0043,0.0171,0.0010</t>
-  </si>
-  <si>
-    <t>0.8126,0.1621,0.0145,0.0029</t>
-  </si>
-  <si>
-    <t>0.9031,0.0533,0.0427,0.0028</t>
-  </si>
-  <si>
-    <t>0.8752,0.1026,0.0110,0.0051</t>
-  </si>
-  <si>
-    <t>0.9654,0.0092,0.0041,0.0047</t>
-  </si>
-  <si>
-    <t>0.9372,0.0194,0.0108,0.0113</t>
-  </si>
-  <si>
-    <t>0.9472,0.0306,0.0095,0.0009</t>
+    <t>0.9818,0.0149,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.9372,0.0215,0.0117,0.0067</t>
+  </si>
+  <si>
+    <t>0.9435,0.0340,0.0029,0.0017</t>
+  </si>
+  <si>
+    <t>0.9693,0.0132,0.0041,0.0016</t>
+  </si>
+  <si>
+    <t>0.9793,0.0103,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9379,0.0417,0.0010,0.0013</t>
+  </si>
+  <si>
+    <t>0.9511,0.0402,0.0027,0.0012</t>
+  </si>
+  <si>
+    <t>0.9220,0.0642,0.0046,0.0016</t>
+  </si>
+  <si>
+    <t>0.8985,0.0859,0.0033,0.0020</t>
+  </si>
+  <si>
+    <t>0.7883,0.2951,0.0048,0.0010</t>
+  </si>
+  <si>
+    <t>0.9056,0.1118,0.0043,0.0014</t>
+  </si>
+  <si>
+    <t>0.8772,0.1101,0.0016,0.0016</t>
+  </si>
+  <si>
+    <t>0.9561,0.0294,0.0077,0.0002</t>
+  </si>
+  <si>
+    <t>0.9593,0.0105,0.0246,0.0004</t>
+  </si>
+  <si>
+    <t>0.9859,0.0042,0.0045,0.0002</t>
+  </si>
+  <si>
+    <t>0.9683,0.0100,0.0189,0.0005</t>
+  </si>
+  <si>
+    <t>0.9108,0.0882,0.0084,0.0006</t>
+  </si>
+  <si>
+    <t>0.7090,0.5705,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.7030,0.4154,0.0111,0.0003</t>
+  </si>
+  <si>
+    <t>0.8226,0.2625,0.0082,0.0005</t>
+  </si>
+  <si>
+    <t>0.8183,0.3368,0.0031,0.0003</t>
+  </si>
+  <si>
+    <t>0.1713,0.9075,0.0046,0.0001</t>
+  </si>
+  <si>
+    <t>0.9761,0.0028,0.0249,0.0006</t>
+  </si>
+  <si>
+    <t>0.9887,0.0037,0.0038,0.0001</t>
+  </si>
+  <si>
+    <t>0.9258,0.0189,0.0734,0.0011</t>
+  </si>
+  <si>
+    <t>0.9343,0.0045,0.1197,0.0007</t>
+  </si>
+  <si>
+    <t>0.9374,0.0041,0.0923,0.0014</t>
+  </si>
+  <si>
+    <t>0.9705,0.0049,0.0241,0.0010</t>
+  </si>
+  <si>
+    <t>0.5689,0.0081,0.5680,0.0019</t>
+  </si>
+  <si>
+    <t>0.7140,0.4130,0.0087,0.0004</t>
+  </si>
+  <si>
+    <t>0.7595,0.2859,0.0137,0.0010</t>
+  </si>
+  <si>
+    <t>0.1583,0.1534,0.7746,0.0063</t>
+  </si>
+  <si>
+    <t>0.2256,0.5875,0.0351,0.0001</t>
+  </si>
+  <si>
+    <t>0.9067,0.0925,0.0045,0.0007</t>
+  </si>
+  <si>
+    <t>0.8828,0.1333,0.0108,0.0007</t>
+  </si>
+  <si>
+    <t>0.7104,0.4619,0.0066,0.0004</t>
+  </si>
+  <si>
+    <t>0.9488,0.0553,0.0052,0.0002</t>
+  </si>
+  <si>
+    <t>0.5522,0.2273,0.0518,0.0007</t>
+  </si>
+  <si>
+    <t>0.9640,0.0026,0.0584,0.0004</t>
+  </si>
+  <si>
+    <t>0.9757,0.0018,0.0271,0.0007</t>
+  </si>
+  <si>
+    <t>0.9886,0.0015,0.0097,0.0003</t>
+  </si>
+  <si>
+    <t>0.9441,0.0010,0.1202,0.0001</t>
+  </si>
+  <si>
+    <t>0.7117,0.1562,0.0398,0.0003</t>
+  </si>
+  <si>
+    <t>0.8811,0.0279,0.1140,0.0084</t>
+  </si>
+  <si>
+    <t>0.9748,0.0168,0.0026,0.0007</t>
+  </si>
+  <si>
+    <t>0.7930,0.3358,0.0023,0.0001</t>
+  </si>
+  <si>
+    <t>0.9890,0.0072,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.5676,0.5631,0.0054,0.0001</t>
+  </si>
+  <si>
+    <t>0.3237,0.0067,0.8031,0.0024</t>
+  </si>
+  <si>
+    <t>0.1592,0.0357,0.8421,0.0021</t>
+  </si>
+  <si>
+    <t>0.9309,0.0102,0.0650,0.0004</t>
+  </si>
+  <si>
+    <t>0.8007,0.0243,0.2367,0.0029</t>
+  </si>
+  <si>
+    <t>0.2384,0.0503,0.7404,0.0018</t>
+  </si>
+  <si>
+    <t>0.8573,0.0053,0.2300,0.0002</t>
+  </si>
+  <si>
+    <t>0.9756,0.0179,0.0023,0.0011</t>
+  </si>
+  <si>
+    <t>0.9225,0.0754,0.0045,0.0007</t>
+  </si>
+  <si>
+    <t>0.8554,0.1658,0.0036,0.0012</t>
+  </si>
+  <si>
+    <t>0.2787,0.5463,0.1659,0.0011</t>
+  </si>
+  <si>
+    <t>0.9587,0.0299,0.0014,0.0010</t>
+  </si>
+  <si>
+    <t>0.9143,0.0956,0.0041,0.0011</t>
+  </si>
+  <si>
+    <t>0.8741,0.1835,0.0046,0.0008</t>
+  </si>
+  <si>
+    <t>0.0555,0.8390,0.4596,0.0004</t>
+  </si>
+  <si>
+    <t>0.3664,0.0376,0.5893,0.0005</t>
+  </si>
+  <si>
+    <t>0.6401,0.0368,0.4189,0.0026</t>
+  </si>
+  <si>
+    <t>0.3806,0.1311,0.1985,0.0002</t>
+  </si>
+  <si>
+    <t>0.9420,0.0032,0.1200,0.0002</t>
+  </si>
+  <si>
+    <t>0.5687,0.5956,0.0053,0.0001</t>
+  </si>
+  <si>
+    <t>0.1286,0.9101,0.0068,0.0001</t>
+  </si>
+  <si>
+    <t>0.9094,0.0485,0.0231,0.0025</t>
+  </si>
+  <si>
+    <t>0.8652,0.1232,0.0163,0.0011</t>
+  </si>
+  <si>
+    <t>0.0640,0.2148,0.8327,0.0028</t>
+  </si>
+  <si>
+    <t>0.7839,0.0318,0.1968,0.0003</t>
+  </si>
+  <si>
+    <t>0.9527,0.0047,0.0668,0.0003</t>
+  </si>
+  <si>
+    <t>0.3849,0.4711,0.1022,0.0014</t>
+  </si>
+  <si>
+    <t>0.5386,0.1259,0.1393,0.0003</t>
+  </si>
+  <si>
+    <t>0.8500,0.0887,0.0514,0.0068</t>
+  </si>
+  <si>
+    <t>0.9368,0.0225,0.0069,0.0074</t>
+  </si>
+  <si>
+    <t>0.9519,0.0142,0.0041,0.0092</t>
+  </si>
+  <si>
+    <t>0.9253,0.0503,0.0038,0.0019</t>
+  </si>
+  <si>
+    <t>0.9656,0.0108,0.0065,0.0041</t>
+  </si>
+  <si>
+    <t>0.9235,0.0627,0.0048,0.0018</t>
+  </si>
+  <si>
+    <t>0.5868,0.4118,0.0303,0.0002</t>
+  </si>
+  <si>
+    <t>0.0892,0.2914,0.9015,0.0009</t>
+  </si>
+  <si>
+    <t>0.6464,0.0722,0.1900,0.0013</t>
+  </si>
+  <si>
+    <t>0.9470,0.0081,0.0828,0.0004</t>
+  </si>
+  <si>
+    <t>0.1130,0.8391,0.0399,0.0001</t>
+  </si>
+  <si>
+    <t>0.8960,0.0270,0.0304,0.0001</t>
+  </si>
+  <si>
+    <t>0.9488,0.0356,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.9419,0.0539,0.0021,0.0012</t>
+  </si>
+  <si>
+    <t>0.7769,0.2613,0.0047,0.0011</t>
+  </si>
+  <si>
+    <t>0.9248,0.1057,0.0033,0.0006</t>
+  </si>
+  <si>
+    <t>0.9393,0.0841,0.0014,0.0003</t>
+  </si>
+  <si>
+    <t>0.9132,0.1112,0.0028,0.0005</t>
+  </si>
+  <si>
+    <t>0.9538,0.0666,0.0016,0.0003</t>
+  </si>
+  <si>
+    <t>0.9784,0.0163,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.9768,0.0167,0.0012,0.0006</t>
+  </si>
+  <si>
+    <t>0.8945,0.1260,0.0039,0.0015</t>
+  </si>
+  <si>
+    <t>0.9736,0.0113,0.0006,0.0012</t>
+  </si>
+  <si>
+    <t>0.9508,0.0432,0.0019,0.0011</t>
+  </si>
+  <si>
+    <t>0.8588,0.1566,0.0056,0.0013</t>
+  </si>
+  <si>
+    <t>0.9295,0.0681,0.0054,0.0014</t>
+  </si>
+  <si>
+    <t>0.9748,0.0160,0.0008,0.0009</t>
+  </si>
+  <si>
+    <t>0.9589,0.0209,0.0013,0.0022</t>
+  </si>
+  <si>
+    <t>0.1868,0.0237,0.8711,0.0014</t>
+  </si>
+  <si>
+    <t>0.8640,0.0126,0.1955,0.0026</t>
+  </si>
+  <si>
+    <t>0.9891,0.0014,0.0065,0.0003</t>
+  </si>
+  <si>
+    <t>0.3160,0.0279,0.7468,0.0033</t>
+  </si>
+  <si>
+    <t>0.6946,0.3908,0.0078,0.0007</t>
+  </si>
+  <si>
+    <t>0.4408,0.6763,0.0177,0.0015</t>
+  </si>
+  <si>
+    <t>0.8632,0.1810,0.0099,0.0005</t>
+  </si>
+  <si>
+    <t>0.9102,0.1231,0.0031,0.0006</t>
+  </si>
+  <si>
+    <t>0.6509,0.4491,0.0103,0.0005</t>
+  </si>
+  <si>
+    <t>0.0927,0.9380,0.0046,0.0004</t>
+  </si>
+  <si>
+    <t>0.8969,0.1470,0.0045,0.0006</t>
+  </si>
+  <si>
+    <t>0.9661,0.0123,0.0073,0.0015</t>
+  </si>
+  <si>
+    <t>0.3606,0.0411,0.6342,0.0126</t>
+  </si>
+  <si>
+    <t>0.9542,0.0162,0.0237,0.0004</t>
+  </si>
+  <si>
+    <t>0.8491,0.0781,0.1012,0.0050</t>
+  </si>
+  <si>
+    <t>0.9422,0.0260,0.0241,0.0024</t>
+  </si>
+  <si>
+    <t>0.9864,0.0121,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.9514,0.0513,0.0025,0.0000</t>
+  </si>
+  <si>
+    <t>0.9005,0.1237,0.0065,0.0003</t>
+  </si>
+  <si>
+    <t>0.5360,0.1673,0.0887,0.0003</t>
+  </si>
+  <si>
+    <t>0.8817,0.2090,0.0024,0.0001</t>
+  </si>
+  <si>
+    <t>0.8930,0.1430,0.0047,0.0004</t>
+  </si>
+  <si>
+    <t>0.8215,0.2091,0.0122,0.0013</t>
+  </si>
+  <si>
+    <t>0.9694,0.0324,0.0021,0.0002</t>
+  </si>
+  <si>
+    <t>0.8892,0.1913,0.0015,0.0003</t>
+  </si>
+  <si>
+    <t>0.8256,0.2659,0.0061,0.0004</t>
+  </si>
+  <si>
+    <t>0.9069,0.0954,0.0069,0.0016</t>
+  </si>
+  <si>
+    <t>0.9477,0.0691,0.0034,0.0005</t>
+  </si>
+  <si>
+    <t>0.9205,0.0951,0.0070,0.0006</t>
+  </si>
+  <si>
+    <t>0.9267,0.0800,0.0030,0.0005</t>
+  </si>
+  <si>
+    <t>0.8484,0.1523,0.0111,0.0023</t>
+  </si>
+  <si>
+    <t>0.7545,0.0113,0.3685,0.0004</t>
+  </si>
+  <si>
+    <t>0.8619,0.0255,0.0781,0.0002</t>
+  </si>
+  <si>
+    <t>0.9599,0.0013,0.0700,0.0001</t>
+  </si>
+  <si>
+    <t>0.8118,0.0229,0.2628,0.0029</t>
+  </si>
+  <si>
+    <t>0.9790,0.0160,0.0035,0.0002</t>
+  </si>
+  <si>
+    <t>0.9892,0.0039,0.0021,0.0002</t>
+  </si>
+  <si>
+    <t>0.8740,0.0418,0.0945,0.0027</t>
+  </si>
+  <si>
+    <t>0.9823,0.0043,0.0031,0.0008</t>
+  </si>
+  <si>
+    <t>0.9232,0.0402,0.0047,0.0031</t>
+  </si>
+  <si>
+    <t>0.9116,0.0107,0.0112,0.0305</t>
+  </si>
+  <si>
+    <t>0.9621,0.0051,0.0105,0.0061</t>
+  </si>
+  <si>
+    <t>0.9888,0.0020,0.0012,0.0016</t>
+  </si>
+  <si>
+    <t>0.1175,0.3570,0.3818,0.0005</t>
+  </si>
+  <si>
+    <t>0.7833,0.2992,0.0105,0.0018</t>
+  </si>
+  <si>
+    <t>0.6406,0.4909,0.0067,0.0010</t>
+  </si>
+  <si>
+    <t>0.7617,0.2992,0.0157,0.0024</t>
+  </si>
+  <si>
+    <t>0.7944,0.2023,0.0194,0.0035</t>
+  </si>
+  <si>
+    <t>0.7709,0.1938,0.0530,0.0069</t>
+  </si>
+  <si>
+    <t>0.9125,0.0771,0.0144,0.0014</t>
+  </si>
+  <si>
+    <t>0.9121,0.0829,0.0026,0.0011</t>
+  </si>
+  <si>
+    <t>0.4252,0.1657,0.5827,0.0172</t>
+  </si>
+  <si>
+    <t>0.9550,0.0179,0.0039,0.0023</t>
+  </si>
+  <si>
+    <t>0.6866,0.3237,0.0117,0.0030</t>
+  </si>
+  <si>
+    <t>0.9010,0.1076,0.0071,0.0005</t>
+  </si>
+  <si>
+    <t>0.9501,0.0441,0.0042,0.0007</t>
+  </si>
+  <si>
+    <t>0.9428,0.0810,0.0022,0.0002</t>
+  </si>
+  <si>
+    <t>0.9709,0.0222,0.0030,0.0001</t>
+  </si>
+  <si>
+    <t>0.9674,0.0210,0.0040,0.0006</t>
+  </si>
+  <si>
+    <t>0.9850,0.0130,0.0014,0.0002</t>
+  </si>
+  <si>
+    <t>0.8957,0.0994,0.0071,0.0021</t>
+  </si>
+  <si>
+    <t>0.8267,0.1742,0.0035,0.0023</t>
+  </si>
+  <si>
+    <t>0.9528,0.0277,0.0021,0.0021</t>
+  </si>
+  <si>
+    <t>0.8347,0.1949,0.0077,0.0019</t>
+  </si>
+  <si>
+    <t>0.9065,0.0820,0.0087,0.0012</t>
+  </si>
+  <si>
+    <t>0.9351,0.0870,0.0019,0.0007</t>
+  </si>
+  <si>
+    <t>0.9185,0.0737,0.0075,0.0020</t>
+  </si>
+  <si>
+    <t>0.9444,0.0261,0.0028,0.0037</t>
+  </si>
+  <si>
+    <t>0.6881,0.4576,0.0043,0.0007</t>
+  </si>
+  <si>
+    <t>0.8841,0.1378,0.0041,0.0005</t>
+  </si>
+  <si>
+    <t>0.7795,0.3428,0.0067,0.0005</t>
+  </si>
+  <si>
+    <t>0.8379,0.1930,0.0054,0.0006</t>
+  </si>
+  <si>
+    <t>0.9492,0.0603,0.0023,0.0004</t>
+  </si>
+  <si>
+    <t>0.9420,0.0567,0.0016,0.0009</t>
+  </si>
+  <si>
+    <t>0.9841,0.0107,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.7383,0.3050,0.0152,0.0020</t>
+  </si>
+  <si>
+    <t>0.0023,0.1056,0.9916,0.0002</t>
+  </si>
+  <si>
+    <t>0.8809,0.1644,0.0055,0.0005</t>
+  </si>
+  <si>
+    <t>0.4192,0.0187,0.6544,0.0012</t>
+  </si>
+  <si>
+    <t>0.8619,0.0150,0.1544,0.0020</t>
+  </si>
+  <si>
+    <t>0.8920,0.0520,0.0283,0.0005</t>
+  </si>
+  <si>
+    <t>0.6110,0.0201,0.4958,0.0003</t>
+  </si>
+  <si>
+    <t>0.9405,0.0182,0.0285,0.0002</t>
+  </si>
+  <si>
+    <t>0.8556,0.0078,0.2144,0.0005</t>
+  </si>
+  <si>
+    <t>0.4350,0.0633,0.4459,0.0015</t>
+  </si>
+  <si>
+    <t>0.9020,0.0481,0.0408,0.0006</t>
+  </si>
+  <si>
+    <t>0.9150,0.0130,0.1001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9343,0.0589,0.0081,0.0005</t>
+  </si>
+  <si>
+    <t>0.9010,0.0742,0.0321,0.0008</t>
+  </si>
+  <si>
+    <t>0.9585,0.0153,0.0146,0.0004</t>
+  </si>
+  <si>
+    <t>0.7021,0.0657,0.2233,0.0022</t>
+  </si>
+  <si>
+    <t>0.9298,0.0310,0.0303,0.0009</t>
+  </si>
+  <si>
+    <t>0.9321,0.0165,0.0507,0.0019</t>
+  </si>
+  <si>
+    <t>0.8196,0.2479,0.0066,0.0010</t>
+  </si>
+  <si>
+    <t>0.8899,0.1606,0.0014,0.0005</t>
+  </si>
+  <si>
+    <t>0.8119,0.3210,0.0036,0.0006</t>
+  </si>
+  <si>
+    <t>0.9445,0.0449,0.0020,0.0010</t>
+  </si>
+  <si>
+    <t>0.9057,0.1093,0.0051,0.0007</t>
+  </si>
+  <si>
+    <t>0.9805,0.0141,0.0029,0.0002</t>
+  </si>
+  <si>
+    <t>0.9812,0.0060,0.0045,0.0003</t>
+  </si>
+  <si>
+    <t>0.9062,0.0823,0.0092,0.0014</t>
+  </si>
+  <si>
+    <t>0.9084,0.0351,0.0513,0.0019</t>
+  </si>
+  <si>
+    <t>0.9163,0.0198,0.0719,0.0026</t>
+  </si>
+  <si>
+    <t>0.5965,0.0507,0.3975,0.0077</t>
+  </si>
+  <si>
+    <t>0.9322,0.0066,0.1106,0.0009</t>
+  </si>
+  <si>
+    <t>0.9492,0.0013,0.0942,0.0005</t>
+  </si>
+  <si>
+    <t>0.9270,0.0111,0.0514,0.0004</t>
+  </si>
+  <si>
+    <t>0.7601,0.1173,0.0364,0.0005</t>
+  </si>
+  <si>
+    <t>0.9214,0.0681,0.0050,0.0022</t>
+  </si>
+  <si>
+    <t>0.9563,0.0350,0.0018,0.0012</t>
+  </si>
+  <si>
+    <t>0.9427,0.0575,0.0014,0.0007</t>
+  </si>
+  <si>
+    <t>0.8335,0.2304,0.0082,0.0009</t>
+  </si>
+  <si>
+    <t>0.9619,0.0361,0.0018,0.0006</t>
+  </si>
+  <si>
+    <t>0.8983,0.1264,0.0032,0.0005</t>
+  </si>
+  <si>
+    <t>0.9431,0.0382,0.0017,0.0013</t>
+  </si>
+  <si>
+    <t>0.9052,0.1120,0.0033,0.0006</t>
+  </si>
+  <si>
+    <t>0.5056,0.2208,0.1553,0.0007</t>
+  </si>
+  <si>
+    <t>0.7283,0.2662,0.0240,0.0007</t>
+  </si>
+  <si>
+    <t>0.8697,0.1012,0.0247,0.0038</t>
+  </si>
+  <si>
+    <t>0.9089,0.0096,0.1244,0.0006</t>
+  </si>
+  <si>
+    <t>0.1503,0.0483,0.8050,0.0065</t>
+  </si>
+  <si>
+    <t>0.7443,0.0642,0.1864,0.0011</t>
+  </si>
+  <si>
+    <t>0.0036,0.0042,0.9960,0.0004</t>
+  </si>
+  <si>
+    <t>0.9351,0.0114,0.0554,0.0006</t>
+  </si>
+  <si>
+    <t>0.0151,0.0766,0.9597,0.0015</t>
+  </si>
+  <si>
+    <t>0.9775,0.0011,0.0465,0.0001</t>
+  </si>
+  <si>
+    <t>0.9286,0.0417,0.0175,0.0004</t>
+  </si>
+  <si>
+    <t>0.9786,0.0085,0.0048,0.0003</t>
+  </si>
+  <si>
+    <t>0.9891,0.0025,0.0048,0.0001</t>
+  </si>
+  <si>
+    <t>0.9311,0.0271,0.0279,0.0014</t>
+  </si>
+  <si>
+    <t>0.8519,0.2410,0.0024,0.0003</t>
+  </si>
+  <si>
+    <t>0.7340,0.4006,0.0025,0.0005</t>
+  </si>
+  <si>
+    <t>0.9418,0.0554,0.0017,0.0006</t>
+  </si>
+  <si>
+    <t>0.9672,0.0440,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9640,0.0289,0.0035,0.0007</t>
+  </si>
+  <si>
+    <t>0.8755,0.1552,0.0048,0.0011</t>
+  </si>
+  <si>
+    <t>0.8985,0.1480,0.0020,0.0005</t>
+  </si>
+  <si>
+    <t>0.9037,0.1253,0.0029,0.0013</t>
+  </si>
+  <si>
+    <t>0.8585,0.0749,0.0337,0.0004</t>
+  </si>
+  <si>
+    <t>0.8130,0.0418,0.1375,0.0016</t>
+  </si>
+  <si>
+    <t>0.5364,0.0251,0.4785,0.0019</t>
+  </si>
+  <si>
+    <t>0.9797,0.0058,0.0110,0.0004</t>
+  </si>
+  <si>
+    <t>0.0543,0.0352,0.9468,0.0007</t>
+  </si>
+  <si>
+    <t>0.9702,0.0072,0.0204,0.0011</t>
+  </si>
+  <si>
+    <t>0.9272,0.0034,0.1484,0.0009</t>
+  </si>
+  <si>
+    <t>0.9698,0.0022,0.0304,0.0002</t>
+  </si>
+  <si>
+    <t>0.9680,0.0131,0.0076,0.0020</t>
+  </si>
+  <si>
+    <t>0.8553,0.0356,0.0949,0.0118</t>
+  </si>
+  <si>
+    <t>0.9816,0.0055,0.0026,0.0019</t>
+  </si>
+  <si>
+    <t>0.8542,0.0551,0.0169,0.0237</t>
+  </si>
+  <si>
+    <t>0.9480,0.0080,0.0027,0.0143</t>
+  </si>
+  <si>
+    <t>0.9480,0.0434,0.0043,0.0005</t>
   </si>
 </sst>
 </file>
@@ -2191,7 +2191,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2345,7 +2345,7 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
         <v>292</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2863,7 +2863,7 @@
         <v>261</v>
       </c>
       <c r="C67" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D67" t="s">
         <v>329</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2933,7 +2933,7 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
         <v>334</v>
@@ -2975,7 +2975,7 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D75" t="s">
         <v>337</v>
@@ -2989,7 +2989,7 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D76" t="s">
         <v>338</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3451,7 +3451,7 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D109" t="s">
         <v>371</v>
@@ -3507,7 +3507,7 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D113" t="s">
         <v>375</v>
@@ -3521,7 +3521,7 @@
         <v>262</v>
       </c>
       <c r="C114" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D114" t="s">
         <v>376</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4445,7 +4445,7 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D180" t="s">
         <v>442</v>
@@ -4459,7 +4459,7 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D181" t="s">
         <v>443</v>
@@ -4529,7 +4529,7 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D186" t="s">
         <v>448</v>
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D187" t="s">
         <v>449</v>
@@ -4557,7 +4557,7 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D188" t="s">
         <v>450</v>
@@ -4711,7 +4711,7 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D199" t="s">
         <v>461</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -5061,7 +5061,7 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D224" t="s">
         <v>486</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5103,7 +5103,7 @@
         <v>261</v>
       </c>
       <c r="C227" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D227" t="s">
         <v>489</v>
@@ -5341,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D244" t="s">
         <v>506</v>
@@ -5355,7 +5355,7 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D245" t="s">
         <v>507</v>
@@ -5383,7 +5383,7 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
         <v>509</v>

--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_80/per_file_predictions_epoch_80.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_80/per_file_predictions_epoch_80.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9818,0.0149,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.9372,0.0215,0.0117,0.0067</t>
-  </si>
-  <si>
-    <t>0.9435,0.0340,0.0029,0.0017</t>
-  </si>
-  <si>
-    <t>0.9693,0.0132,0.0041,0.0016</t>
-  </si>
-  <si>
-    <t>0.9793,0.0103,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.9379,0.0417,0.0010,0.0013</t>
-  </si>
-  <si>
-    <t>0.9511,0.0402,0.0027,0.0012</t>
-  </si>
-  <si>
-    <t>0.9220,0.0642,0.0046,0.0016</t>
-  </si>
-  <si>
-    <t>0.8985,0.0859,0.0033,0.0020</t>
-  </si>
-  <si>
-    <t>0.7883,0.2951,0.0048,0.0010</t>
-  </si>
-  <si>
-    <t>0.9056,0.1118,0.0043,0.0014</t>
-  </si>
-  <si>
-    <t>0.8772,0.1101,0.0016,0.0016</t>
-  </si>
-  <si>
-    <t>0.9561,0.0294,0.0077,0.0002</t>
-  </si>
-  <si>
-    <t>0.9593,0.0105,0.0246,0.0004</t>
-  </si>
-  <si>
-    <t>0.9859,0.0042,0.0045,0.0002</t>
-  </si>
-  <si>
-    <t>0.9683,0.0100,0.0189,0.0005</t>
-  </si>
-  <si>
-    <t>0.9108,0.0882,0.0084,0.0006</t>
-  </si>
-  <si>
-    <t>0.7090,0.5705,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.7030,0.4154,0.0111,0.0003</t>
-  </si>
-  <si>
-    <t>0.8226,0.2625,0.0082,0.0005</t>
-  </si>
-  <si>
-    <t>0.8183,0.3368,0.0031,0.0003</t>
-  </si>
-  <si>
-    <t>0.1713,0.9075,0.0046,0.0001</t>
-  </si>
-  <si>
-    <t>0.9761,0.0028,0.0249,0.0006</t>
-  </si>
-  <si>
-    <t>0.9887,0.0037,0.0038,0.0001</t>
-  </si>
-  <si>
-    <t>0.9258,0.0189,0.0734,0.0011</t>
-  </si>
-  <si>
-    <t>0.9343,0.0045,0.1197,0.0007</t>
-  </si>
-  <si>
-    <t>0.9374,0.0041,0.0923,0.0014</t>
-  </si>
-  <si>
-    <t>0.9705,0.0049,0.0241,0.0010</t>
-  </si>
-  <si>
-    <t>0.5689,0.0081,0.5680,0.0019</t>
-  </si>
-  <si>
-    <t>0.7140,0.4130,0.0087,0.0004</t>
-  </si>
-  <si>
-    <t>0.7595,0.2859,0.0137,0.0010</t>
-  </si>
-  <si>
-    <t>0.1583,0.1534,0.7746,0.0063</t>
-  </si>
-  <si>
-    <t>0.2256,0.5875,0.0351,0.0001</t>
-  </si>
-  <si>
-    <t>0.9067,0.0925,0.0045,0.0007</t>
-  </si>
-  <si>
-    <t>0.8828,0.1333,0.0108,0.0007</t>
-  </si>
-  <si>
-    <t>0.7104,0.4619,0.0066,0.0004</t>
-  </si>
-  <si>
-    <t>0.9488,0.0553,0.0052,0.0002</t>
-  </si>
-  <si>
-    <t>0.5522,0.2273,0.0518,0.0007</t>
-  </si>
-  <si>
-    <t>0.9640,0.0026,0.0584,0.0004</t>
-  </si>
-  <si>
-    <t>0.9757,0.0018,0.0271,0.0007</t>
-  </si>
-  <si>
-    <t>0.9886,0.0015,0.0097,0.0003</t>
-  </si>
-  <si>
-    <t>0.9441,0.0010,0.1202,0.0001</t>
-  </si>
-  <si>
-    <t>0.7117,0.1562,0.0398,0.0003</t>
-  </si>
-  <si>
-    <t>0.8811,0.0279,0.1140,0.0084</t>
-  </si>
-  <si>
-    <t>0.9748,0.0168,0.0026,0.0007</t>
-  </si>
-  <si>
-    <t>0.7930,0.3358,0.0023,0.0001</t>
-  </si>
-  <si>
-    <t>0.9890,0.0072,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.5676,0.5631,0.0054,0.0001</t>
-  </si>
-  <si>
-    <t>0.3237,0.0067,0.8031,0.0024</t>
-  </si>
-  <si>
-    <t>0.1592,0.0357,0.8421,0.0021</t>
-  </si>
-  <si>
-    <t>0.9309,0.0102,0.0650,0.0004</t>
-  </si>
-  <si>
-    <t>0.8007,0.0243,0.2367,0.0029</t>
-  </si>
-  <si>
-    <t>0.2384,0.0503,0.7404,0.0018</t>
-  </si>
-  <si>
-    <t>0.8573,0.0053,0.2300,0.0002</t>
-  </si>
-  <si>
-    <t>0.9756,0.0179,0.0023,0.0011</t>
-  </si>
-  <si>
-    <t>0.9225,0.0754,0.0045,0.0007</t>
-  </si>
-  <si>
-    <t>0.8554,0.1658,0.0036,0.0012</t>
-  </si>
-  <si>
-    <t>0.2787,0.5463,0.1659,0.0011</t>
-  </si>
-  <si>
-    <t>0.9587,0.0299,0.0014,0.0010</t>
-  </si>
-  <si>
-    <t>0.9143,0.0956,0.0041,0.0011</t>
-  </si>
-  <si>
-    <t>0.8741,0.1835,0.0046,0.0008</t>
-  </si>
-  <si>
-    <t>0.0555,0.8390,0.4596,0.0004</t>
-  </si>
-  <si>
-    <t>0.3664,0.0376,0.5893,0.0005</t>
-  </si>
-  <si>
-    <t>0.6401,0.0368,0.4189,0.0026</t>
-  </si>
-  <si>
-    <t>0.3806,0.1311,0.1985,0.0002</t>
-  </si>
-  <si>
-    <t>0.9420,0.0032,0.1200,0.0002</t>
-  </si>
-  <si>
-    <t>0.5687,0.5956,0.0053,0.0001</t>
-  </si>
-  <si>
-    <t>0.1286,0.9101,0.0068,0.0001</t>
-  </si>
-  <si>
-    <t>0.9094,0.0485,0.0231,0.0025</t>
-  </si>
-  <si>
-    <t>0.8652,0.1232,0.0163,0.0011</t>
-  </si>
-  <si>
-    <t>0.0640,0.2148,0.8327,0.0028</t>
-  </si>
-  <si>
-    <t>0.7839,0.0318,0.1968,0.0003</t>
-  </si>
-  <si>
-    <t>0.9527,0.0047,0.0668,0.0003</t>
-  </si>
-  <si>
-    <t>0.3849,0.4711,0.1022,0.0014</t>
-  </si>
-  <si>
-    <t>0.5386,0.1259,0.1393,0.0003</t>
-  </si>
-  <si>
-    <t>0.8500,0.0887,0.0514,0.0068</t>
-  </si>
-  <si>
-    <t>0.9368,0.0225,0.0069,0.0074</t>
-  </si>
-  <si>
-    <t>0.9519,0.0142,0.0041,0.0092</t>
-  </si>
-  <si>
-    <t>0.9253,0.0503,0.0038,0.0019</t>
-  </si>
-  <si>
-    <t>0.9656,0.0108,0.0065,0.0041</t>
-  </si>
-  <si>
-    <t>0.9235,0.0627,0.0048,0.0018</t>
-  </si>
-  <si>
-    <t>0.5868,0.4118,0.0303,0.0002</t>
-  </si>
-  <si>
-    <t>0.0892,0.2914,0.9015,0.0009</t>
-  </si>
-  <si>
-    <t>0.6464,0.0722,0.1900,0.0013</t>
-  </si>
-  <si>
-    <t>0.9470,0.0081,0.0828,0.0004</t>
-  </si>
-  <si>
-    <t>0.1130,0.8391,0.0399,0.0001</t>
-  </si>
-  <si>
-    <t>0.8960,0.0270,0.0304,0.0001</t>
-  </si>
-  <si>
-    <t>0.9488,0.0356,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.9419,0.0539,0.0021,0.0012</t>
-  </si>
-  <si>
-    <t>0.7769,0.2613,0.0047,0.0011</t>
-  </si>
-  <si>
-    <t>0.9248,0.1057,0.0033,0.0006</t>
-  </si>
-  <si>
-    <t>0.9393,0.0841,0.0014,0.0003</t>
-  </si>
-  <si>
-    <t>0.9132,0.1112,0.0028,0.0005</t>
-  </si>
-  <si>
-    <t>0.9538,0.0666,0.0016,0.0003</t>
-  </si>
-  <si>
-    <t>0.9784,0.0163,0.0008,0.0005</t>
-  </si>
-  <si>
-    <t>0.9768,0.0167,0.0012,0.0006</t>
-  </si>
-  <si>
-    <t>0.8945,0.1260,0.0039,0.0015</t>
-  </si>
-  <si>
-    <t>0.9736,0.0113,0.0006,0.0012</t>
-  </si>
-  <si>
-    <t>0.9508,0.0432,0.0019,0.0011</t>
-  </si>
-  <si>
-    <t>0.8588,0.1566,0.0056,0.0013</t>
-  </si>
-  <si>
-    <t>0.9295,0.0681,0.0054,0.0014</t>
-  </si>
-  <si>
-    <t>0.9748,0.0160,0.0008,0.0009</t>
-  </si>
-  <si>
-    <t>0.9589,0.0209,0.0013,0.0022</t>
-  </si>
-  <si>
-    <t>0.1868,0.0237,0.8711,0.0014</t>
-  </si>
-  <si>
-    <t>0.8640,0.0126,0.1955,0.0026</t>
-  </si>
-  <si>
-    <t>0.9891,0.0014,0.0065,0.0003</t>
-  </si>
-  <si>
-    <t>0.3160,0.0279,0.7468,0.0033</t>
-  </si>
-  <si>
-    <t>0.6946,0.3908,0.0078,0.0007</t>
-  </si>
-  <si>
-    <t>0.4408,0.6763,0.0177,0.0015</t>
-  </si>
-  <si>
-    <t>0.8632,0.1810,0.0099,0.0005</t>
-  </si>
-  <si>
-    <t>0.9102,0.1231,0.0031,0.0006</t>
-  </si>
-  <si>
-    <t>0.6509,0.4491,0.0103,0.0005</t>
-  </si>
-  <si>
-    <t>0.0927,0.9380,0.0046,0.0004</t>
-  </si>
-  <si>
-    <t>0.8969,0.1470,0.0045,0.0006</t>
-  </si>
-  <si>
-    <t>0.9661,0.0123,0.0073,0.0015</t>
-  </si>
-  <si>
-    <t>0.3606,0.0411,0.6342,0.0126</t>
-  </si>
-  <si>
-    <t>0.9542,0.0162,0.0237,0.0004</t>
-  </si>
-  <si>
-    <t>0.8491,0.0781,0.1012,0.0050</t>
-  </si>
-  <si>
-    <t>0.9422,0.0260,0.0241,0.0024</t>
-  </si>
-  <si>
-    <t>0.9864,0.0121,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.9514,0.0513,0.0025,0.0000</t>
-  </si>
-  <si>
-    <t>0.9005,0.1237,0.0065,0.0003</t>
-  </si>
-  <si>
-    <t>0.5360,0.1673,0.0887,0.0003</t>
-  </si>
-  <si>
-    <t>0.8817,0.2090,0.0024,0.0001</t>
-  </si>
-  <si>
-    <t>0.8930,0.1430,0.0047,0.0004</t>
-  </si>
-  <si>
-    <t>0.8215,0.2091,0.0122,0.0013</t>
-  </si>
-  <si>
-    <t>0.9694,0.0324,0.0021,0.0002</t>
-  </si>
-  <si>
-    <t>0.8892,0.1913,0.0015,0.0003</t>
-  </si>
-  <si>
-    <t>0.8256,0.2659,0.0061,0.0004</t>
-  </si>
-  <si>
-    <t>0.9069,0.0954,0.0069,0.0016</t>
-  </si>
-  <si>
-    <t>0.9477,0.0691,0.0034,0.0005</t>
-  </si>
-  <si>
-    <t>0.9205,0.0951,0.0070,0.0006</t>
-  </si>
-  <si>
-    <t>0.9267,0.0800,0.0030,0.0005</t>
-  </si>
-  <si>
-    <t>0.8484,0.1523,0.0111,0.0023</t>
-  </si>
-  <si>
-    <t>0.7545,0.0113,0.3685,0.0004</t>
-  </si>
-  <si>
-    <t>0.8619,0.0255,0.0781,0.0002</t>
-  </si>
-  <si>
-    <t>0.9599,0.0013,0.0700,0.0001</t>
-  </si>
-  <si>
-    <t>0.8118,0.0229,0.2628,0.0029</t>
-  </si>
-  <si>
-    <t>0.9790,0.0160,0.0035,0.0002</t>
-  </si>
-  <si>
-    <t>0.9892,0.0039,0.0021,0.0002</t>
-  </si>
-  <si>
-    <t>0.8740,0.0418,0.0945,0.0027</t>
-  </si>
-  <si>
-    <t>0.9823,0.0043,0.0031,0.0008</t>
-  </si>
-  <si>
-    <t>0.9232,0.0402,0.0047,0.0031</t>
-  </si>
-  <si>
-    <t>0.9116,0.0107,0.0112,0.0305</t>
-  </si>
-  <si>
-    <t>0.9621,0.0051,0.0105,0.0061</t>
-  </si>
-  <si>
-    <t>0.9888,0.0020,0.0012,0.0016</t>
-  </si>
-  <si>
-    <t>0.1175,0.3570,0.3818,0.0005</t>
-  </si>
-  <si>
-    <t>0.7833,0.2992,0.0105,0.0018</t>
-  </si>
-  <si>
-    <t>0.6406,0.4909,0.0067,0.0010</t>
-  </si>
-  <si>
-    <t>0.7617,0.2992,0.0157,0.0024</t>
-  </si>
-  <si>
-    <t>0.7944,0.2023,0.0194,0.0035</t>
-  </si>
-  <si>
-    <t>0.7709,0.1938,0.0530,0.0069</t>
-  </si>
-  <si>
-    <t>0.9125,0.0771,0.0144,0.0014</t>
-  </si>
-  <si>
-    <t>0.9121,0.0829,0.0026,0.0011</t>
-  </si>
-  <si>
-    <t>0.4252,0.1657,0.5827,0.0172</t>
-  </si>
-  <si>
-    <t>0.9550,0.0179,0.0039,0.0023</t>
-  </si>
-  <si>
-    <t>0.6866,0.3237,0.0117,0.0030</t>
-  </si>
-  <si>
-    <t>0.9010,0.1076,0.0071,0.0005</t>
-  </si>
-  <si>
-    <t>0.9501,0.0441,0.0042,0.0007</t>
-  </si>
-  <si>
-    <t>0.9428,0.0810,0.0022,0.0002</t>
-  </si>
-  <si>
-    <t>0.9709,0.0222,0.0030,0.0001</t>
-  </si>
-  <si>
-    <t>0.9674,0.0210,0.0040,0.0006</t>
-  </si>
-  <si>
-    <t>0.9850,0.0130,0.0014,0.0002</t>
-  </si>
-  <si>
-    <t>0.8957,0.0994,0.0071,0.0021</t>
-  </si>
-  <si>
-    <t>0.8267,0.1742,0.0035,0.0023</t>
-  </si>
-  <si>
-    <t>0.9528,0.0277,0.0021,0.0021</t>
-  </si>
-  <si>
-    <t>0.8347,0.1949,0.0077,0.0019</t>
-  </si>
-  <si>
-    <t>0.9065,0.0820,0.0087,0.0012</t>
-  </si>
-  <si>
-    <t>0.9351,0.0870,0.0019,0.0007</t>
-  </si>
-  <si>
-    <t>0.9185,0.0737,0.0075,0.0020</t>
-  </si>
-  <si>
-    <t>0.9444,0.0261,0.0028,0.0037</t>
-  </si>
-  <si>
-    <t>0.6881,0.4576,0.0043,0.0007</t>
-  </si>
-  <si>
-    <t>0.8841,0.1378,0.0041,0.0005</t>
-  </si>
-  <si>
-    <t>0.7795,0.3428,0.0067,0.0005</t>
-  </si>
-  <si>
-    <t>0.8379,0.1930,0.0054,0.0006</t>
-  </si>
-  <si>
-    <t>0.9492,0.0603,0.0023,0.0004</t>
-  </si>
-  <si>
-    <t>0.9420,0.0567,0.0016,0.0009</t>
-  </si>
-  <si>
-    <t>0.9841,0.0107,0.0009,0.0006</t>
-  </si>
-  <si>
-    <t>0.7383,0.3050,0.0152,0.0020</t>
-  </si>
-  <si>
-    <t>0.0023,0.1056,0.9916,0.0002</t>
-  </si>
-  <si>
-    <t>0.8809,0.1644,0.0055,0.0005</t>
-  </si>
-  <si>
-    <t>0.4192,0.0187,0.6544,0.0012</t>
-  </si>
-  <si>
-    <t>0.8619,0.0150,0.1544,0.0020</t>
-  </si>
-  <si>
-    <t>0.8920,0.0520,0.0283,0.0005</t>
-  </si>
-  <si>
-    <t>0.6110,0.0201,0.4958,0.0003</t>
-  </si>
-  <si>
-    <t>0.9405,0.0182,0.0285,0.0002</t>
-  </si>
-  <si>
-    <t>0.8556,0.0078,0.2144,0.0005</t>
-  </si>
-  <si>
-    <t>0.4350,0.0633,0.4459,0.0015</t>
-  </si>
-  <si>
-    <t>0.9020,0.0481,0.0408,0.0006</t>
-  </si>
-  <si>
-    <t>0.9150,0.0130,0.1001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9343,0.0589,0.0081,0.0005</t>
-  </si>
-  <si>
-    <t>0.9010,0.0742,0.0321,0.0008</t>
-  </si>
-  <si>
-    <t>0.9585,0.0153,0.0146,0.0004</t>
-  </si>
-  <si>
-    <t>0.7021,0.0657,0.2233,0.0022</t>
-  </si>
-  <si>
-    <t>0.9298,0.0310,0.0303,0.0009</t>
-  </si>
-  <si>
-    <t>0.9321,0.0165,0.0507,0.0019</t>
-  </si>
-  <si>
-    <t>0.8196,0.2479,0.0066,0.0010</t>
-  </si>
-  <si>
-    <t>0.8899,0.1606,0.0014,0.0005</t>
-  </si>
-  <si>
-    <t>0.8119,0.3210,0.0036,0.0006</t>
-  </si>
-  <si>
-    <t>0.9445,0.0449,0.0020,0.0010</t>
-  </si>
-  <si>
-    <t>0.9057,0.1093,0.0051,0.0007</t>
-  </si>
-  <si>
-    <t>0.9805,0.0141,0.0029,0.0002</t>
-  </si>
-  <si>
-    <t>0.9812,0.0060,0.0045,0.0003</t>
-  </si>
-  <si>
-    <t>0.9062,0.0823,0.0092,0.0014</t>
-  </si>
-  <si>
-    <t>0.9084,0.0351,0.0513,0.0019</t>
-  </si>
-  <si>
-    <t>0.9163,0.0198,0.0719,0.0026</t>
-  </si>
-  <si>
-    <t>0.5965,0.0507,0.3975,0.0077</t>
-  </si>
-  <si>
-    <t>0.9322,0.0066,0.1106,0.0009</t>
-  </si>
-  <si>
-    <t>0.9492,0.0013,0.0942,0.0005</t>
-  </si>
-  <si>
-    <t>0.9270,0.0111,0.0514,0.0004</t>
-  </si>
-  <si>
-    <t>0.7601,0.1173,0.0364,0.0005</t>
-  </si>
-  <si>
-    <t>0.9214,0.0681,0.0050,0.0022</t>
-  </si>
-  <si>
-    <t>0.9563,0.0350,0.0018,0.0012</t>
-  </si>
-  <si>
-    <t>0.9427,0.0575,0.0014,0.0007</t>
-  </si>
-  <si>
-    <t>0.8335,0.2304,0.0082,0.0009</t>
-  </si>
-  <si>
-    <t>0.9619,0.0361,0.0018,0.0006</t>
-  </si>
-  <si>
-    <t>0.8983,0.1264,0.0032,0.0005</t>
-  </si>
-  <si>
-    <t>0.9431,0.0382,0.0017,0.0013</t>
-  </si>
-  <si>
-    <t>0.9052,0.1120,0.0033,0.0006</t>
-  </si>
-  <si>
-    <t>0.5056,0.2208,0.1553,0.0007</t>
-  </si>
-  <si>
-    <t>0.7283,0.2662,0.0240,0.0007</t>
-  </si>
-  <si>
-    <t>0.8697,0.1012,0.0247,0.0038</t>
-  </si>
-  <si>
-    <t>0.9089,0.0096,0.1244,0.0006</t>
-  </si>
-  <si>
-    <t>0.1503,0.0483,0.8050,0.0065</t>
-  </si>
-  <si>
-    <t>0.7443,0.0642,0.1864,0.0011</t>
-  </si>
-  <si>
-    <t>0.0036,0.0042,0.9960,0.0004</t>
-  </si>
-  <si>
-    <t>0.9351,0.0114,0.0554,0.0006</t>
-  </si>
-  <si>
-    <t>0.0151,0.0766,0.9597,0.0015</t>
-  </si>
-  <si>
-    <t>0.9775,0.0011,0.0465,0.0001</t>
-  </si>
-  <si>
-    <t>0.9286,0.0417,0.0175,0.0004</t>
-  </si>
-  <si>
-    <t>0.9786,0.0085,0.0048,0.0003</t>
-  </si>
-  <si>
-    <t>0.9891,0.0025,0.0048,0.0001</t>
-  </si>
-  <si>
-    <t>0.9311,0.0271,0.0279,0.0014</t>
-  </si>
-  <si>
-    <t>0.8519,0.2410,0.0024,0.0003</t>
-  </si>
-  <si>
-    <t>0.7340,0.4006,0.0025,0.0005</t>
-  </si>
-  <si>
-    <t>0.9418,0.0554,0.0017,0.0006</t>
-  </si>
-  <si>
-    <t>0.9672,0.0440,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9640,0.0289,0.0035,0.0007</t>
-  </si>
-  <si>
-    <t>0.8755,0.1552,0.0048,0.0011</t>
-  </si>
-  <si>
-    <t>0.8985,0.1480,0.0020,0.0005</t>
-  </si>
-  <si>
-    <t>0.9037,0.1253,0.0029,0.0013</t>
-  </si>
-  <si>
-    <t>0.8585,0.0749,0.0337,0.0004</t>
-  </si>
-  <si>
-    <t>0.8130,0.0418,0.1375,0.0016</t>
-  </si>
-  <si>
-    <t>0.5364,0.0251,0.4785,0.0019</t>
-  </si>
-  <si>
-    <t>0.9797,0.0058,0.0110,0.0004</t>
-  </si>
-  <si>
-    <t>0.0543,0.0352,0.9468,0.0007</t>
-  </si>
-  <si>
-    <t>0.9702,0.0072,0.0204,0.0011</t>
-  </si>
-  <si>
-    <t>0.9272,0.0034,0.1484,0.0009</t>
-  </si>
-  <si>
-    <t>0.9698,0.0022,0.0304,0.0002</t>
-  </si>
-  <si>
-    <t>0.9680,0.0131,0.0076,0.0020</t>
-  </si>
-  <si>
-    <t>0.8553,0.0356,0.0949,0.0118</t>
-  </si>
-  <si>
-    <t>0.9816,0.0055,0.0026,0.0019</t>
-  </si>
-  <si>
-    <t>0.8542,0.0551,0.0169,0.0237</t>
-  </si>
-  <si>
-    <t>0.9480,0.0080,0.0027,0.0143</t>
-  </si>
-  <si>
-    <t>0.9480,0.0434,0.0043,0.0005</t>
+    <t>0.9223,0.0213,0.0082,0.0291</t>
+  </si>
+  <si>
+    <t>0.0153,0.0015,0.0007,0.9932</t>
+  </si>
+  <si>
+    <t>0.8794,0.0016,0.0002,0.1356</t>
+  </si>
+  <si>
+    <t>0.3613,0.0041,0.0033,0.8177</t>
+  </si>
+  <si>
+    <t>0.9984,0.0002,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9976,0.0004,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9963,0.0008,0.0003,0.0012</t>
+  </si>
+  <si>
+    <t>0.9981,0.0002,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.9920,0.0058,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.9938,0.0025,0.0013,0.0007</t>
+  </si>
+  <si>
+    <t>0.9968,0.0008,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9971,0.0008,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9543,0.0037,0.0627,0.0014</t>
+  </si>
+  <si>
+    <t>0.1912,0.0029,0.8399,0.0087</t>
+  </si>
+  <si>
+    <t>0.2068,0.0048,0.9021,0.0006</t>
+  </si>
+  <si>
+    <t>0.2535,0.0015,0.8555,0.0009</t>
+  </si>
+  <si>
+    <t>0.9731,0.0038,0.0306,0.0006</t>
+  </si>
+  <si>
+    <t>0.0027,0.9954,0.0024,0.0004</t>
+  </si>
+  <si>
+    <t>0.0037,0.9932,0.0020,0.0020</t>
+  </si>
+  <si>
+    <t>0.1367,0.8983,0.0293,0.0030</t>
+  </si>
+  <si>
+    <t>0.0030,0.9936,0.0050,0.0015</t>
+  </si>
+  <si>
+    <t>0.0156,0.9795,0.0150,0.0016</t>
+  </si>
+  <si>
+    <t>0.8127,0.0063,0.3176,0.0022</t>
+  </si>
+  <si>
+    <t>0.7243,0.0068,0.3642,0.0083</t>
+  </si>
+  <si>
+    <t>0.0207,0.0023,0.9726,0.0047</t>
+  </si>
+  <si>
+    <t>0.2712,0.0275,0.6886,0.0108</t>
+  </si>
+  <si>
+    <t>0.0715,0.0015,0.9601,0.0009</t>
+  </si>
+  <si>
+    <t>0.0337,0.0095,0.9405,0.0143</t>
+  </si>
+  <si>
+    <t>0.0058,0.0007,0.9918,0.0011</t>
+  </si>
+  <si>
+    <t>0.2584,0.8137,0.0084,0.0116</t>
+  </si>
+  <si>
+    <t>0.2941,0.4875,0.3495,0.0160</t>
+  </si>
+  <si>
+    <t>0.0037,0.0408,0.9916,0.0057</t>
+  </si>
+  <si>
+    <t>0.0106,0.9710,0.0286,0.0001</t>
+  </si>
+  <si>
+    <t>0.9690,0.0175,0.0060,0.0039</t>
+  </si>
+  <si>
+    <t>0.6047,0.2634,0.1296,0.0194</t>
+  </si>
+  <si>
+    <t>0.5502,0.6725,0.0028,0.0004</t>
+  </si>
+  <si>
+    <t>0.0121,0.9781,0.0756,0.0004</t>
+  </si>
+  <si>
+    <t>0.0189,0.0947,0.9178,0.0180</t>
+  </si>
+  <si>
+    <t>0.2170,0.0147,0.8894,0.0032</t>
+  </si>
+  <si>
+    <t>0.1260,0.0160,0.9032,0.0038</t>
+  </si>
+  <si>
+    <t>0.0248,0.0022,0.9416,0.0297</t>
+  </si>
+  <si>
+    <t>0.0018,0.6506,0.9918,0.0005</t>
+  </si>
+  <si>
+    <t>0.0027,0.5306,0.5995,0.0007</t>
+  </si>
+  <si>
+    <t>0.0064,0.0054,0.9861,0.0037</t>
+  </si>
+  <si>
+    <t>0.4127,0.5375,0.0017,0.0386</t>
+  </si>
+  <si>
+    <t>0.0003,0.9980,0.0018,0.0015</t>
+  </si>
+  <si>
+    <t>0.0220,0.9115,0.0618,0.0267</t>
+  </si>
+  <si>
+    <t>0.0127,0.9730,0.0220,0.0033</t>
+  </si>
+  <si>
+    <t>0.0004,0.0034,0.9968,0.0027</t>
+  </si>
+  <si>
+    <t>0.0011,0.0100,0.9958,0.0011</t>
+  </si>
+  <si>
+    <t>0.0048,0.0016,0.9856,0.0069</t>
+  </si>
+  <si>
+    <t>0.0143,0.0122,0.9840,0.0013</t>
+  </si>
+  <si>
+    <t>0.0057,0.0334,0.9884,0.0022</t>
+  </si>
+  <si>
+    <t>0.0079,0.0218,0.9769,0.0056</t>
+  </si>
+  <si>
+    <t>0.9593,0.0532,0.0017,0.0017</t>
+  </si>
+  <si>
+    <t>0.9779,0.0168,0.0046,0.0013</t>
+  </si>
+  <si>
+    <t>0.9925,0.0023,0.0005,0.0023</t>
+  </si>
+  <si>
+    <t>0.0387,0.0583,0.9626,0.0058</t>
+  </si>
+  <si>
+    <t>0.9954,0.0010,0.0015,0.0008</t>
+  </si>
+  <si>
+    <t>0.9902,0.0063,0.0011,0.0012</t>
+  </si>
+  <si>
+    <t>0.9882,0.0177,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.0005,0.9798,0.9860,0.0002</t>
+  </si>
+  <si>
+    <t>0.0066,0.0029,0.9915,0.0023</t>
+  </si>
+  <si>
+    <t>0.0053,0.0038,0.9911,0.0024</t>
+  </si>
+  <si>
+    <t>0.0012,0.9638,0.9545,0.0007</t>
+  </si>
+  <si>
+    <t>0.0020,0.0036,0.9958,0.0015</t>
+  </si>
+  <si>
+    <t>0.0533,0.9437,0.0170,0.0006</t>
+  </si>
+  <si>
+    <t>0.0018,0.9966,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.2073,0.0184,0.8873,0.0029</t>
+  </si>
+  <si>
+    <t>0.1855,0.3712,0.6183,0.0038</t>
+  </si>
+  <si>
+    <t>0.0056,0.0122,0.9867,0.0197</t>
+  </si>
+  <si>
+    <t>0.0006,0.9861,0.9161,0.0001</t>
+  </si>
+  <si>
+    <t>0.0076,0.8797,0.7614,0.0015</t>
+  </si>
+  <si>
+    <t>0.0009,0.9920,0.3894,0.0014</t>
+  </si>
+  <si>
+    <t>0.0004,0.9774,0.9551,0.0002</t>
+  </si>
+  <si>
+    <t>0.0071,0.0001,0.0083,0.9908</t>
+  </si>
+  <si>
+    <t>0.0018,0.0154,0.0015,0.9971</t>
+  </si>
+  <si>
+    <t>0.0061,0.0014,0.0002,0.9975</t>
+  </si>
+  <si>
+    <t>0.0030,0.0141,0.0011,0.9968</t>
+  </si>
+  <si>
+    <t>0.0018,0.0021,0.0009,0.9981</t>
+  </si>
+  <si>
+    <t>0.0026,0.0495,0.0011,0.9961</t>
+  </si>
+  <si>
+    <t>0.0024,0.9741,0.7507,0.0009</t>
+  </si>
+  <si>
+    <t>0.0045,0.0715,0.9916,0.0011</t>
+  </si>
+  <si>
+    <t>0.0086,0.9396,0.3209,0.0081</t>
+  </si>
+  <si>
+    <t>0.0009,0.2430,0.9960,0.0004</t>
+  </si>
+  <si>
+    <t>0.0003,0.9934,0.5749,0.0001</t>
+  </si>
+  <si>
+    <t>0.0067,0.9703,0.1300,0.0033</t>
+  </si>
+  <si>
+    <t>0.9919,0.0029,0.0012,0.0021</t>
+  </si>
+  <si>
+    <t>0.9963,0.0029,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.8338,0.3105,0.0020,0.0011</t>
+  </si>
+  <si>
+    <t>0.9916,0.0054,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.9955,0.0031,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9961,0.0007,0.0002,0.0016</t>
+  </si>
+  <si>
+    <t>0.9903,0.0052,0.0016,0.0017</t>
+  </si>
+  <si>
+    <t>0.9926,0.0098,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9983,0.0001,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9973,0.0011,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9981,0.0008,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9989,0.0002,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9979,0.0005,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9932,0.0036,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9961,0.0023,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9973,0.0004,0.0004,0.0014</t>
+  </si>
+  <si>
+    <t>0.0092,0.0094,0.9905,0.0008</t>
+  </si>
+  <si>
+    <t>0.0084,0.0016,0.9904,0.0011</t>
+  </si>
+  <si>
+    <t>0.8889,0.0047,0.1561,0.0071</t>
+  </si>
+  <si>
+    <t>0.0072,0.0015,0.9912,0.0009</t>
+  </si>
+  <si>
+    <t>0.0053,0.9922,0.0013,0.0007</t>
+  </si>
+  <si>
+    <t>0.0019,0.9950,0.0014,0.0006</t>
+  </si>
+  <si>
+    <t>0.0178,0.9810,0.0028,0.0017</t>
+  </si>
+  <si>
+    <t>0.0445,0.9666,0.0024,0.0023</t>
+  </si>
+  <si>
+    <t>0.0049,0.9920,0.0020,0.0005</t>
+  </si>
+  <si>
+    <t>0.0035,0.9924,0.0048,0.0004</t>
+  </si>
+  <si>
+    <t>0.6857,0.5712,0.0017,0.0005</t>
+  </si>
+  <si>
+    <t>0.7439,0.0958,0.0955,0.0447</t>
+  </si>
+  <si>
+    <t>0.1609,0.0016,0.8602,0.0079</t>
+  </si>
+  <si>
+    <t>0.4587,0.0461,0.4987,0.0620</t>
+  </si>
+  <si>
+    <t>0.4679,0.0113,0.6865,0.0046</t>
+  </si>
+  <si>
+    <t>0.0351,0.0914,0.0499,0.9336</t>
+  </si>
+  <si>
+    <t>0.0087,0.9905,0.0017,0.0005</t>
+  </si>
+  <si>
+    <t>0.0025,0.9917,0.0127,0.0012</t>
+  </si>
+  <si>
+    <t>0.0016,0.9943,0.0025,0.0017</t>
+  </si>
+  <si>
+    <t>0.0006,0.3658,0.9902,0.0006</t>
+  </si>
+  <si>
+    <t>0.0018,0.9960,0.0020,0.0001</t>
+  </si>
+  <si>
+    <t>0.8423,0.0917,0.0797,0.0062</t>
+  </si>
+  <si>
+    <t>0.6086,0.3308,0.0800,0.0021</t>
+  </si>
+  <si>
+    <t>0.9638,0.0280,0.0083,0.0031</t>
+  </si>
+  <si>
+    <t>0.9897,0.0015,0.0030,0.0035</t>
+  </si>
+  <si>
+    <t>0.9922,0.0010,0.0009,0.0027</t>
+  </si>
+  <si>
+    <t>0.9844,0.0049,0.0085,0.0013</t>
+  </si>
+  <si>
+    <t>0.9974,0.0001,0.0008,0.0010</t>
+  </si>
+  <si>
+    <t>0.9932,0.0011,0.0032,0.0019</t>
+  </si>
+  <si>
+    <t>0.9958,0.0007,0.0005,0.0011</t>
+  </si>
+  <si>
+    <t>0.9905,0.0032,0.0027,0.0018</t>
+  </si>
+  <si>
+    <t>0.0011,0.8684,0.9840,0.0010</t>
+  </si>
+  <si>
+    <t>0.0043,0.6510,0.9578,0.0014</t>
+  </si>
+  <si>
+    <t>0.0152,0.0053,0.9749,0.0031</t>
+  </si>
+  <si>
+    <t>0.0110,0.5229,0.8885,0.0021</t>
+  </si>
+  <si>
+    <t>0.9901,0.0016,0.0069,0.0005</t>
+  </si>
+  <si>
+    <t>0.6954,0.0097,0.2749,0.0210</t>
+  </si>
+  <si>
+    <t>0.1792,0.0040,0.8866,0.0024</t>
+  </si>
+  <si>
+    <t>0.9200,0.0136,0.0570,0.0086</t>
+  </si>
+  <si>
+    <t>0.1705,0.0005,0.0009,0.9554</t>
+  </si>
+  <si>
+    <t>0.0008,0.0080,0.0014,0.9984</t>
+  </si>
+  <si>
+    <t>0.0003,0.0573,0.0009,0.9985</t>
+  </si>
+  <si>
+    <t>0.0047,0.0001,0.0011,0.9973</t>
+  </si>
+  <si>
+    <t>0.0011,0.9950,0.0496,0.0003</t>
+  </si>
+  <si>
+    <t>0.9969,0.0007,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.0953,0.9230,0.0054,0.0073</t>
+  </si>
+  <si>
+    <t>0.9966,0.0008,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.7908,0.3231,0.0034,0.0018</t>
+  </si>
+  <si>
+    <t>0.9911,0.0015,0.0007,0.0025</t>
+  </si>
+  <si>
+    <t>0.8660,0.0125,0.0022,0.1024</t>
+  </si>
+  <si>
+    <t>0.9956,0.0012,0.0015,0.0004</t>
+  </si>
+  <si>
+    <t>0.0050,0.0156,0.9769,0.0434</t>
+  </si>
+  <si>
+    <t>0.9864,0.0004,0.0004,0.0167</t>
+  </si>
+  <si>
+    <t>0.9859,0.0019,0.0015,0.0054</t>
+  </si>
+  <si>
+    <t>0.3400,0.6450,0.0945,0.0079</t>
+  </si>
+  <si>
+    <t>0.9735,0.0081,0.0032,0.0066</t>
+  </si>
+  <si>
+    <t>0.9868,0.0063,0.0041,0.0008</t>
+  </si>
+  <si>
+    <t>0.2610,0.7018,0.0716,0.0491</t>
+  </si>
+  <si>
+    <t>0.9732,0.0191,0.0031,0.0008</t>
+  </si>
+  <si>
+    <t>0.9753,0.0200,0.0036,0.0011</t>
+  </si>
+  <si>
+    <t>0.9979,0.0007,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9962,0.0025,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9951,0.0020,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9969,0.0001,0.0013,0.0007</t>
+  </si>
+  <si>
+    <t>0.9949,0.0007,0.0016,0.0010</t>
+  </si>
+  <si>
+    <t>0.9725,0.0226,0.0044,0.0011</t>
+  </si>
+  <si>
+    <t>0.9950,0.0008,0.0021,0.0010</t>
+  </si>
+  <si>
+    <t>0.9961,0.0004,0.0004,0.0014</t>
+  </si>
+  <si>
+    <t>0.8429,0.1804,0.0018,0.0052</t>
+  </si>
+  <si>
+    <t>0.7243,0.4416,0.0025,0.0009</t>
+  </si>
+  <si>
+    <t>0.6221,0.5451,0.0061,0.0008</t>
+  </si>
+  <si>
+    <t>0.3167,0.6827,0.1093,0.0083</t>
+  </si>
+  <si>
+    <t>0.9905,0.0114,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.7289,0.2817,0.0489,0.0126</t>
+  </si>
+  <si>
+    <t>0.9948,0.0025,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.9325,0.0678,0.0010,0.0052</t>
+  </si>
+  <si>
+    <t>0.0007,0.0109,0.9988,0.0005</t>
+  </si>
+  <si>
+    <t>0.9441,0.0456,0.0156,0.0037</t>
+  </si>
+  <si>
+    <t>0.0031,0.0028,0.9937,0.0010</t>
+  </si>
+  <si>
+    <t>0.0020,0.0442,0.9937,0.0021</t>
+  </si>
+  <si>
+    <t>0.0087,0.0050,0.9879,0.0026</t>
+  </si>
+  <si>
+    <t>0.0052,0.0705,0.9865,0.0045</t>
+  </si>
+  <si>
+    <t>0.0018,0.0130,0.9919,0.0036</t>
+  </si>
+  <si>
+    <t>0.0013,0.0038,0.9972,0.0009</t>
+  </si>
+  <si>
+    <t>0.0063,0.0158,0.9865,0.0049</t>
+  </si>
+  <si>
+    <t>0.0213,0.0100,0.9614,0.0041</t>
+  </si>
+  <si>
+    <t>0.1305,0.0579,0.6998,0.2466</t>
+  </si>
+  <si>
+    <t>0.0118,0.0093,0.9848,0.0008</t>
+  </si>
+  <si>
+    <t>0.0368,0.8903,0.1155,0.0048</t>
+  </si>
+  <si>
+    <t>0.0591,0.7668,0.1492,0.0025</t>
+  </si>
+  <si>
+    <t>0.8795,0.0205,0.1202,0.0058</t>
+  </si>
+  <si>
+    <t>0.5493,0.0075,0.4333,0.0335</t>
+  </si>
+  <si>
+    <t>0.1820,0.0689,0.7482,0.0097</t>
+  </si>
+  <si>
+    <t>0.0130,0.9866,0.0027,0.0017</t>
+  </si>
+  <si>
+    <t>0.0096,0.9902,0.0018,0.0019</t>
+  </si>
+  <si>
+    <t>0.8143,0.3614,0.0009,0.0016</t>
+  </si>
+  <si>
+    <t>0.9723,0.0497,0.0016,0.0002</t>
+  </si>
+  <si>
+    <t>0.8744,0.1912,0.0032,0.0027</t>
+  </si>
+  <si>
+    <t>0.6639,0.0206,0.3903,0.0111</t>
+  </si>
+  <si>
+    <t>0.9205,0.0073,0.0806,0.0053</t>
+  </si>
+  <si>
+    <t>0.9471,0.0075,0.0125,0.0088</t>
+  </si>
+  <si>
+    <t>0.7601,0.0131,0.3351,0.0097</t>
+  </si>
+  <si>
+    <t>0.1737,0.0040,0.6588,0.1068</t>
+  </si>
+  <si>
+    <t>0.0044,0.0021,0.9915,0.0029</t>
+  </si>
+  <si>
+    <t>0.0081,0.0229,0.9751,0.0028</t>
+  </si>
+  <si>
+    <t>0.0170,0.0305,0.9721,0.0058</t>
+  </si>
+  <si>
+    <t>0.1127,0.0332,0.8484,0.0041</t>
+  </si>
+  <si>
+    <t>0.0174,0.0310,0.9817,0.0011</t>
+  </si>
+  <si>
+    <t>0.9960,0.0015,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9937,0.0031,0.0015,0.0004</t>
+  </si>
+  <si>
+    <t>0.9746,0.0219,0.0039,0.0011</t>
+  </si>
+  <si>
+    <t>0.9981,0.0006,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9449,0.0705,0.0034,0.0021</t>
+  </si>
+  <si>
+    <t>0.9936,0.0046,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9906,0.0082,0.0010,0.0007</t>
+  </si>
+  <si>
+    <t>0.9968,0.0005,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.0072,0.2778,0.9859,0.0048</t>
+  </si>
+  <si>
+    <t>0.0254,0.7188,0.4996,0.0022</t>
+  </si>
+  <si>
+    <t>0.6885,0.0155,0.1835,0.0503</t>
+  </si>
+  <si>
+    <t>0.0069,0.0011,0.9946,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.0033,0.9926,0.0106</t>
+  </si>
+  <si>
+    <t>0.0015,0.0482,0.9882,0.0038</t>
+  </si>
+  <si>
+    <t>0.0013,0.0087,0.9990,0.0001</t>
+  </si>
+  <si>
+    <t>0.0062,0.0012,0.9905,0.0008</t>
+  </si>
+  <si>
+    <t>0.0040,0.0024,0.9914,0.0029</t>
+  </si>
+  <si>
+    <t>0.0042,0.0212,0.9883,0.0015</t>
+  </si>
+  <si>
+    <t>0.0078,0.1012,0.9575,0.0092</t>
+  </si>
+  <si>
+    <t>0.7274,0.0090,0.3163,0.0164</t>
+  </si>
+  <si>
+    <t>0.8116,0.0034,0.3340,0.0009</t>
+  </si>
+  <si>
+    <t>0.8999,0.0166,0.0825,0.0159</t>
+  </si>
+  <si>
+    <t>0.9899,0.0087,0.0009,0.0009</t>
+  </si>
+  <si>
+    <t>0.9954,0.0019,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.9982,0.0003,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9879,0.0073,0.0021,0.0013</t>
+  </si>
+  <si>
+    <t>0.9958,0.0006,0.0004,0.0019</t>
+  </si>
+  <si>
+    <t>0.9969,0.0014,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9868,0.0071,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.9958,0.0012,0.0015,0.0007</t>
+  </si>
+  <si>
+    <t>0.0057,0.1000,0.9597,0.0011</t>
+  </si>
+  <si>
+    <t>0.0018,0.1262,0.9938,0.0004</t>
+  </si>
+  <si>
+    <t>0.0189,0.0167,0.9586,0.0064</t>
+  </si>
+  <si>
+    <t>0.0507,0.0702,0.8911,0.0206</t>
+  </si>
+  <si>
+    <t>0.0727,0.0013,0.9564,0.0006</t>
+  </si>
+  <si>
+    <t>0.0307,0.0403,0.8763,0.1931</t>
+  </si>
+  <si>
+    <t>0.6876,0.0108,0.3760,0.0104</t>
+  </si>
+  <si>
+    <t>0.0136,0.0111,0.9566,0.0177</t>
+  </si>
+  <si>
+    <t>0.9658,0.0011,0.0036,0.0236</t>
+  </si>
+  <si>
+    <t>0.0782,0.0046,0.0113,0.9584</t>
+  </si>
+  <si>
+    <t>0.1097,0.0005,0.0001,0.9745</t>
+  </si>
+  <si>
+    <t>0.0010,0.0000,0.0003,0.9993</t>
+  </si>
+  <si>
+    <t>0.0024,0.0007,0.0007,0.9984</t>
+  </si>
+  <si>
+    <t>0.9678,0.0051,0.0025,0.0083</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2149,7 +2149,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>278</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2205,7 +2205,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2233,7 +2233,7 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D22" t="s">
         <v>284</v>
@@ -2289,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2317,7 +2317,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2359,7 +2359,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
         <v>293</v>
@@ -2443,7 +2443,7 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
         <v>299</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2485,7 +2485,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
         <v>302</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2513,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2569,7 +2569,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D46" t="s">
         <v>308</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2695,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2835,7 +2835,7 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
         <v>327</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2863,7 +2863,7 @@
         <v>261</v>
       </c>
       <c r="C67" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D67" t="s">
         <v>329</v>
@@ -2905,7 +2905,7 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D70" t="s">
         <v>332</v>
@@ -2919,7 +2919,7 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
         <v>333</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -2975,7 +2975,7 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
         <v>337</v>
@@ -2989,7 +2989,7 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
         <v>338</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3087,7 +3087,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
         <v>345</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3157,7 +3157,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3409,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3451,7 +3451,7 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D109" t="s">
         <v>371</v>
@@ -3479,7 +3479,7 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
         <v>373</v>
@@ -3493,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3507,7 +3507,7 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
         <v>375</v>
@@ -3535,7 +3535,7 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
         <v>377</v>
@@ -3591,7 +3591,7 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
         <v>381</v>
@@ -3605,7 +3605,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>382</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3633,7 +3633,7 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
         <v>384</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3661,7 +3661,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3857,7 +3857,7 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
         <v>400</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3955,7 +3955,7 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
         <v>407</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4151,7 +4151,7 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
         <v>421</v>
@@ -4193,7 +4193,7 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
         <v>424</v>
@@ -4375,7 +4375,7 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
         <v>437</v>
@@ -4389,7 +4389,7 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D176" t="s">
         <v>438</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4529,7 +4529,7 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D186" t="s">
         <v>448</v>
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
         <v>449</v>
@@ -4557,7 +4557,7 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D188" t="s">
         <v>450</v>
@@ -4571,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
         <v>451</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4613,7 +4613,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
         <v>454</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4641,7 +4641,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
         <v>456</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4697,7 +4697,7 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
         <v>460</v>
@@ -4711,7 +4711,7 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
         <v>461</v>
@@ -4823,7 +4823,7 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
         <v>469</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
         <v>474</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5061,7 +5061,7 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D224" t="s">
         <v>486</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5145,7 +5145,7 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
         <v>492</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5341,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D244" t="s">
         <v>506</v>
@@ -5355,7 +5355,7 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
         <v>507</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5397,7 +5397,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
         <v>510</v>
@@ -5425,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
         <v>512</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
